--- a/data/bakgrund.xlsx
+++ b/data/bakgrund.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://svenskidrott-my.sharepoint.com/personal/william_lind_rfsisu_se/Documents/Dokument/GitHub/Hemsideprojekt/Hemsideprojekt/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://svenskidrott-my.sharepoint.com/personal/william_lind_rfsisu_se/Documents/Dokument/GitHub/RF-SISU Uppland/sverige-i-siffror/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_5ECA8A2D2F12AADE0878375E75B60769C0037583" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A79675-FBD8-4554-AC33-26B7B098ADBC}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_5ECA8A2D2F12AADE0878375E75B60769C0037583" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BB53136-5B7D-465D-A81C-F57393780DFB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="000001NU" sheetId="2" r:id="rId1"/>
@@ -184,11 +184,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,13 +490,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z45"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AA45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="26" width="9.1796875" customWidth="1"/>
+    <col min="1" max="26" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>40</v>
       </c>
@@ -576,15 +575,18 @@
       <c r="Z1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="AA1" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="2">
@@ -656,15 +658,18 @@
       <c r="Z2" s="2">
         <v>153719</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="AA2" s="2">
+        <v>148360</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="2">
@@ -736,15 +741,18 @@
       <c r="Z3" s="2">
         <v>145816</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="AA3" s="2">
+        <v>141085</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="2">
@@ -816,15 +824,18 @@
       <c r="Z4" s="2">
         <v>178483</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="AA4" s="2">
+        <v>179623</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="2">
@@ -896,15 +907,18 @@
       <c r="Z5" s="2">
         <v>166349</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="AA5" s="2">
+        <v>167040</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="2">
@@ -976,15 +990,18 @@
       <c r="Z6" s="2">
         <v>220892</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="AA6" s="2">
+        <v>218585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="2">
@@ -1056,15 +1073,18 @@
       <c r="Z7" s="2">
         <v>198035</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="AA7" s="2">
+        <v>199221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="2">
@@ -1136,15 +1156,18 @@
       <c r="Z8" s="2">
         <v>267466</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="AA8" s="2">
+        <v>264012</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="2">
@@ -1216,15 +1239,18 @@
       <c r="Z9" s="2">
         <v>257698</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="AA9" s="2">
+        <v>257175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>25</v>
       </c>
       <c r="D10" s="2">
@@ -1296,15 +1322,18 @@
       <c r="Z10" s="2">
         <v>238560</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="AA10" s="2">
+        <v>244717</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="2">
@@ -1376,15 +1405,18 @@
       <c r="Z11" s="2">
         <v>232956</v>
       </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="AA11" s="2">
+        <v>238901</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="2">
@@ -1456,15 +1488,18 @@
       <c r="Z12" s="2">
         <v>175473</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="AA12" s="2">
+        <v>178841</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="2">
@@ -1536,15 +1571,18 @@
       <c r="Z13" s="2">
         <v>181477</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="AA13" s="2">
+        <v>185853</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="2">
@@ -1616,15 +1654,18 @@
       <c r="Z14" s="2">
         <v>126757</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="AA14" s="2">
+        <v>131498</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" t="s">
         <v>26</v>
       </c>
       <c r="D15" s="2">
@@ -1696,15 +1737,18 @@
       <c r="Z15" s="2">
         <v>132003</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="AA15" s="2">
+        <v>136617</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" t="s">
         <v>25</v>
       </c>
       <c r="D16" s="2">
@@ -1776,15 +1820,18 @@
       <c r="Z16" s="2">
         <v>71156</v>
       </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="AA16" s="2">
+        <v>74263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="2">
@@ -1856,15 +1903,18 @@
       <c r="Z17" s="2">
         <v>84709</v>
       </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="AA17" s="2">
+        <v>88396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="2">
@@ -1936,15 +1986,18 @@
       <c r="Z18" s="2">
         <v>29132</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+      <c r="AA18" s="2">
+        <v>30383</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" t="s">
         <v>26</v>
       </c>
       <c r="D19" s="2">
@@ -2016,15 +2069,18 @@
       <c r="Z19" s="2">
         <v>37338</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="AA19" s="2">
+        <v>38829</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="2">
@@ -2096,15 +2152,18 @@
       <c r="Z20" s="2">
         <v>3560</v>
       </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+      <c r="AA20" s="2">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21" s="2">
@@ -2176,15 +2235,18 @@
       <c r="Z21" s="2">
         <v>8904</v>
       </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
+      <c r="AA21" s="2">
+        <v>9189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="2">
@@ -2256,15 +2318,18 @@
       <c r="Z22" s="2">
         <v>80</v>
       </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
+      <c r="AA22" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" t="s">
         <v>26</v>
       </c>
       <c r="D23" s="2">
@@ -2336,15 +2401,18 @@
       <c r="Z23" s="2">
         <v>314</v>
       </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
+      <c r="AA23" s="2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" t="s">
         <v>25</v>
       </c>
       <c r="D24" s="2">
@@ -2416,15 +2484,18 @@
       <c r="Z24" s="2">
         <v>435939</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
+      <c r="AA24" s="2">
+        <v>427224</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" t="s">
         <v>26</v>
       </c>
       <c r="D25" s="2">
@@ -2496,15 +2567,18 @@
       <c r="Z25" s="2">
         <v>411854</v>
       </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
+      <c r="AA25" s="2">
+        <v>404256</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="2">
@@ -2576,15 +2650,18 @@
       <c r="Z26" s="2">
         <v>467200</v>
       </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
+      <c r="AA26" s="2">
+        <v>469096</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" t="s">
         <v>26</v>
       </c>
       <c r="D27" s="2">
@@ -2656,15 +2733,18 @@
       <c r="Z27" s="2">
         <v>442139</v>
       </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
+      <c r="AA27" s="2">
+        <v>443072</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="2">
@@ -2736,15 +2816,18 @@
       <c r="Z28" s="2">
         <v>415444</v>
       </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
+      <c r="AA28" s="2">
+        <v>413936</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" t="s">
         <v>26</v>
       </c>
       <c r="D29" s="2">
@@ -2816,15 +2899,18 @@
       <c r="Z29" s="2">
         <v>390370</v>
       </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
+      <c r="AA29" s="2">
+        <v>389102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" t="s">
         <v>25</v>
       </c>
       <c r="D30" s="2">
@@ -2896,15 +2982,18 @@
       <c r="Z30" s="2">
         <v>503459</v>
       </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
+      <c r="AA30" s="2">
+        <v>502938</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" t="s">
         <v>26</v>
       </c>
       <c r="D31" s="2">
@@ -2976,15 +3065,18 @@
       <c r="Z31" s="2">
         <v>478448</v>
       </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
+      <c r="AA31" s="2">
+        <v>478230</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" t="s">
         <v>25</v>
       </c>
       <c r="D32" s="2">
@@ -3056,15 +3148,18 @@
       <c r="Z32" s="2">
         <v>423782</v>
       </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
+      <c r="AA32" s="2">
+        <v>421259</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="2">
@@ -3136,15 +3231,18 @@
       <c r="Z33" s="2">
         <v>403671</v>
       </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
+      <c r="AA33" s="2">
+        <v>401260</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" t="s">
         <v>25</v>
       </c>
       <c r="D34" s="2">
@@ -3216,15 +3314,18 @@
       <c r="Z34" s="2">
         <v>502408</v>
       </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
+      <c r="AA34" s="2">
+        <v>493422</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" t="s">
         <v>26</v>
       </c>
       <c r="D35" s="2">
@@ -3296,15 +3397,18 @@
       <c r="Z35" s="2">
         <v>481102</v>
       </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
+      <c r="AA35" s="2">
+        <v>472518</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="2">
@@ -3376,15 +3480,18 @@
       <c r="Z36" s="2">
         <v>451557</v>
       </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
+      <c r="AA36" s="2">
+        <v>459234</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" t="s">
         <v>26</v>
       </c>
       <c r="D37" s="2">
@@ -3456,15 +3563,18 @@
       <c r="Z37" s="2">
         <v>446571</v>
       </c>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
+      <c r="AA37" s="2">
+        <v>453079</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="2">
@@ -3536,15 +3646,18 @@
       <c r="Z38" s="2">
         <v>416505</v>
       </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
+      <c r="AA38" s="2">
+        <v>408812</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" t="s">
         <v>26</v>
       </c>
       <c r="D39" s="2">
@@ -3616,15 +3729,18 @@
       <c r="Z39" s="2">
         <v>438066</v>
       </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
+      <c r="AA39" s="2">
+        <v>429948</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" t="s">
         <v>25</v>
       </c>
       <c r="D40" s="2">
@@ -3696,15 +3812,18 @@
       <c r="Z40" s="2">
         <v>213450</v>
       </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
+      <c r="AA40" s="2">
+        <v>229171</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" t="s">
         <v>34</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" t="s">
         <v>26</v>
       </c>
       <c r="D41" s="2">
@@ -3776,15 +3895,18 @@
       <c r="Z41" s="2">
         <v>263198</v>
       </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A42" s="3" t="s">
+      <c r="AA41" s="2">
+        <v>278309</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" t="s">
         <v>25</v>
       </c>
       <c r="D42" s="2">
@@ -3856,15 +3978,18 @@
       <c r="Z42" s="2">
         <v>29310</v>
       </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
+      <c r="AA42" s="2">
+        <v>30758</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" t="s">
         <v>26</v>
       </c>
       <c r="D43" s="2">
@@ -3936,15 +4061,18 @@
       <c r="Z43" s="2">
         <v>59793</v>
       </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
+      <c r="AA43" s="2">
+        <v>60435</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>37</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" t="s">
         <v>25</v>
       </c>
       <c r="D44" s="2">
@@ -4016,15 +4144,18 @@
       <c r="Z44" s="2">
         <v>453</v>
       </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
+      <c r="AA44" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" t="s">
         <v>36</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" t="s">
         <v>26</v>
       </c>
       <c r="D45" s="2">
@@ -4096,14 +4227,18 @@
       <c r="Z45" s="2">
         <v>2114</v>
       </c>
+      <c r="AA45" s="2">
+        <v>2142</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="9" orientation="landscape" copies="5" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{eb5b2d6e-028e-454d-b878-0c055adbeb2a}" enabled="0" method="" siteId="{eb5b2d6e-028e-454d-b878-0c055adbeb2a}" removed="1"/>
+  <clbl:label id="{e782e157-8ece-4105-b8e9-fe1eecbfcd69}" enabled="1" method="Privileged" siteId="{eb5b2d6e-028e-454d-b878-0c055adbeb2a}" removed="0"/>
 </clbl:labelList>
 </file>